--- a/artfynd/A 10292-2023 artfynd.xlsx
+++ b/artfynd/A 10292-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10292-2023 artfynd.xlsx
+++ b/artfynd/A 10292-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7242772</v>
+        <v>7242771</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618472.0823297722</v>
+        <v>618415</v>
       </c>
       <c r="R2" t="n">
-        <v>7108060.802111281</v>
+        <v>7107964</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,11 +763,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # asp</t>
+          <t>2 substratenheter # sälg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7242771</v>
+        <v>7242772</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618415.2545291435</v>
+        <v>618472</v>
       </c>
       <c r="R3" t="n">
-        <v>7107964.02976083</v>
+        <v>7108061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,21 +857,11 @@
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -907,11 +877,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # sälg</t>
+          <t>1 substratenheter # asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7242778</v>
+        <v>7242776</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618583.5130073733</v>
+        <v>618631</v>
       </c>
       <c r="R4" t="n">
-        <v>7107646.321355701</v>
+        <v>7107752</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,19 +971,9 @@
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,15 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7242777</v>
+        <v>7242778</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618631.2321013741</v>
+        <v>618584</v>
       </c>
       <c r="R5" t="n">
-        <v>7107751.957036297</v>
+        <v>7107646</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,19 +1085,9 @@
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1109,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # levande gran</t>
+          <t>1 substratenheter # sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1191,15 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7242776</v>
+        <v>7242781</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618631.2321013741</v>
+        <v>618524</v>
       </c>
       <c r="R6" t="n">
-        <v>7107751.957036297</v>
+        <v>7107551</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,21 +1199,11 @@
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1290,7 +1215,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AN6" t="n">

--- a/artfynd/A 10292-2023 artfynd.xlsx
+++ b/artfynd/A 10292-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7242771</v>
+        <v>134600593</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borgfäbodarna, Ås lm</t>
+          <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618415</v>
+        <v>618261</v>
       </c>
       <c r="R2" t="n">
-        <v>7107964</v>
+        <v>7107786</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,81 +766,68 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>2 substratenheter # sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7242772</v>
+        <v>134600616</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>91937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borgfäbodarna, Ås lm</t>
+          <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618472</v>
+        <v>618445</v>
       </c>
       <c r="R3" t="n">
-        <v>7108061</v>
+        <v>7108029</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,81 +877,68 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asp</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson, Sture Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7242776</v>
+        <v>134600592</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Borgfäbodarna, Ås lm</t>
+          <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618631</v>
+        <v>618251</v>
       </c>
       <c r="R4" t="n">
-        <v>7107752</v>
+        <v>7107755</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,12 +962,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,81 +988,68 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # sälg</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7242778</v>
+        <v>134600596</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Borgfäbodarna, Ås lm</t>
+          <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618584</v>
+        <v>618278</v>
       </c>
       <c r="R5" t="n">
-        <v>7107646</v>
+        <v>7107864</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1073,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,81 +1099,68 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # sälg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7242781</v>
+        <v>134600605</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Borgfäbodarna, Ås lm</t>
+          <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618524</v>
+        <v>618392</v>
       </c>
       <c r="R6" t="n">
-        <v>7107551</v>
+        <v>7107934</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,12 +1184,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,34 +1210,4217 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # sälg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134600619</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>618494</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7108103</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134600620</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>618550</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7108120</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134600625</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>618508</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7107896</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134600591</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>618239</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7107716</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134600601</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>618345</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7107902</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134600618</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>618493</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7108108</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7242771</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Borgfäbodarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>618415</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7107964</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>2 substratenheter # sälg</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Niina Sallmén</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Niina Sallmén</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7242772</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Borgfäbodarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>618472</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7108061</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asp</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7242776</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Borgfäbodarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>618631</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7107752</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7242778</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Borgfäbodarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>618584</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7107646</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7242781</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Borgfäbodarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>618524</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7107551</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134600590</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>618228</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7107710</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134600595</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>618278</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7107860</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134600598</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>618272</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7107899</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134600606</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>618395</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7107952</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134600608</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>618409</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7107953</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134600609</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>618413</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7107963</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134600611</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>618445</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7108000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134600613</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>618448</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7108002</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134600597</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>618280</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7107895</v>
+      </c>
+      <c r="S26" t="n">
+        <v>77</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134600600</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>618343</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7107901</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134600604</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>618391</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7107940</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134600607</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>618395</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7107952</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134600612</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>618445</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7107999</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134600617</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>618484</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7108085</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134600621</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>618571</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7108018</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134600622</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>618510</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7107948</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134600623</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>618504</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7107921</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134600624</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>618502</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7107915</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134600626</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>618506</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7107873</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134600627</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>618494</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7107769</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134600614</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>618441</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7108023</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134600599</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>618328</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7107905</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134600629</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>618484</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7107716</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134600602</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>618350</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7107906</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134600603</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>618369</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7107927</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134600610</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>618432</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7107994</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 10292-2023 artfynd.xlsx
+++ b/artfynd/A 10292-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,48 +1563,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134600591</v>
+        <v>134767608</v>
       </c>
       <c r="B10" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pellemyrtjärnen, Ås lm</t>
+          <t>Pellemyrtjärnen, Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618239</v>
+        <v>618163</v>
       </c>
       <c r="R10" t="n">
-        <v>7107716</v>
+        <v>7107770</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,22 +1628,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:57</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:57</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,26 +1648,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134600601</v>
+        <v>134600591</v>
       </c>
       <c r="B11" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,21 +1671,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618345</v>
+        <v>618239</v>
       </c>
       <c r="R11" t="n">
-        <v>7107902</v>
+        <v>7107716</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1771,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134600618</v>
+        <v>134600601</v>
       </c>
       <c r="B12" t="n">
         <v>79992</v>
@@ -1820,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618493</v>
+        <v>618345</v>
       </c>
       <c r="R12" t="n">
-        <v>7108108</v>
+        <v>7107902</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1855,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,7 +1871,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1896,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7242771</v>
+        <v>134600618</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>79992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,37 +1893,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Borgfäbodarna, Ås lm</t>
+          <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618415</v>
+        <v>618493</v>
       </c>
       <c r="R13" t="n">
-        <v>7107964</v>
+        <v>7108108</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,12 +1947,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2013-09-18</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,40 +1973,27 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>2 substratenheter # sälg</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Alva Danielsson, Sture Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7242772</v>
+        <v>7242771</v>
       </c>
       <c r="B14" t="n">
         <v>80432</v>
@@ -2045,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618472</v>
+        <v>618415</v>
       </c>
       <c r="R14" t="n">
-        <v>7108061</v>
+        <v>7107964</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,11 +2081,11 @@
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # asp</t>
+          <t>2 substratenheter # sälg</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2124,7 +2107,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7242776</v>
+        <v>7242772</v>
       </c>
       <c r="B15" t="n">
         <v>80432</v>
@@ -2159,13 +2142,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618631</v>
+        <v>618472</v>
       </c>
       <c r="R15" t="n">
-        <v>7107752</v>
+        <v>7108061</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2208,7 +2191,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2216,7 +2199,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # sälg</t>
+          <t>1 substratenheter # asp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,7 +2221,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7242778</v>
+        <v>7242776</v>
       </c>
       <c r="B16" t="n">
         <v>80432</v>
@@ -2273,13 +2256,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618584</v>
+        <v>618631</v>
       </c>
       <c r="R16" t="n">
-        <v>7107646</v>
+        <v>7107752</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2352,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7242781</v>
+        <v>7242778</v>
       </c>
       <c r="B17" t="n">
         <v>80432</v>
@@ -2387,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618524</v>
+        <v>618584</v>
       </c>
       <c r="R17" t="n">
-        <v>7107551</v>
+        <v>7107646</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,7 +2419,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2466,10 +2449,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134600590</v>
+        <v>7242781</v>
       </c>
       <c r="B18" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,17 +2480,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pellemyrtjärnen, Ås lm</t>
+          <t>Borgfäbodarna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618228</v>
+        <v>618524</v>
       </c>
       <c r="R18" t="n">
-        <v>7107710</v>
+        <v>7107551</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2531,22 +2514,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2013-09-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2013-09-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,27 +2530,40 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134600595</v>
+        <v>134600590</v>
       </c>
       <c r="B19" t="n">
         <v>80488</v>
@@ -2612,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618278</v>
+        <v>618228</v>
       </c>
       <c r="R19" t="n">
-        <v>7107860</v>
+        <v>7107710</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,7 +2633,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2657,7 +2643,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2688,7 +2674,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134600598</v>
+        <v>134600595</v>
       </c>
       <c r="B20" t="n">
         <v>80488</v>
@@ -2723,13 +2709,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618272</v>
+        <v>618278</v>
       </c>
       <c r="R20" t="n">
-        <v>7107899</v>
+        <v>7107860</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2758,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2768,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2799,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134600606</v>
+        <v>134600598</v>
       </c>
       <c r="B21" t="n">
         <v>80488</v>
@@ -2834,13 +2820,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618395</v>
+        <v>618272</v>
       </c>
       <c r="R21" t="n">
-        <v>7107952</v>
+        <v>7107899</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2869,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2879,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2910,7 +2896,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134600608</v>
+        <v>134600606</v>
       </c>
       <c r="B22" t="n">
         <v>80488</v>
@@ -2945,13 +2931,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618409</v>
+        <v>618395</v>
       </c>
       <c r="R22" t="n">
-        <v>7107953</v>
+        <v>7107952</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2980,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2990,7 +2976,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3021,7 +3007,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134600609</v>
+        <v>134600608</v>
       </c>
       <c r="B23" t="n">
         <v>80488</v>
@@ -3050,26 +3036,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618413</v>
+        <v>618409</v>
       </c>
       <c r="R23" t="n">
-        <v>7107963</v>
+        <v>7107953</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,7 +3077,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3108,7 +3087,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3117,24 +3096,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3155,7 +3118,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134600611</v>
+        <v>134600609</v>
       </c>
       <c r="B24" t="n">
         <v>80488</v>
@@ -3184,16 +3147,23 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618445</v>
+        <v>618413</v>
       </c>
       <c r="R24" t="n">
-        <v>7108000</v>
+        <v>7107963</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3225,7 +3195,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3205,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3244,8 +3214,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3255,7 +3241,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3266,32 +3252,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134600613</v>
+        <v>134600611</v>
       </c>
       <c r="B25" t="n">
-        <v>80499</v>
+        <v>80488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3287,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618448</v>
+        <v>618445</v>
       </c>
       <c r="R25" t="n">
-        <v>7108002</v>
+        <v>7108000</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3336,7 +3322,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3332,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,48 +3363,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134600597</v>
+        <v>134767657</v>
       </c>
       <c r="B26" t="n">
-        <v>80500</v>
+        <v>80488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pellemyrtjärnen, Ås lm</t>
+          <t>Pellemyrtjärnen, Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618280</v>
+        <v>618170</v>
       </c>
       <c r="R26" t="n">
-        <v>7107895</v>
+        <v>7107804</v>
       </c>
       <c r="S26" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3442,22 +3428,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3472,61 +3448,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134600600</v>
+        <v>134767677</v>
       </c>
       <c r="B27" t="n">
-        <v>80500</v>
+        <v>80488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pellemyrtjärnen, Ås lm</t>
+          <t>Pellemyrtjärnen, Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618343</v>
+        <v>618195</v>
       </c>
       <c r="R27" t="n">
-        <v>7107901</v>
+        <v>7107779</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3553,22 +3525,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3583,26 +3545,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134600604</v>
+        <v>134600613</v>
       </c>
       <c r="B28" t="n">
-        <v>80500</v>
+        <v>80499</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3610,21 +3568,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3634,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618391</v>
+        <v>618448</v>
       </c>
       <c r="R28" t="n">
-        <v>7107940</v>
+        <v>7108002</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3669,7 +3627,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3637,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,7 +3657,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Sture Gustafsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3710,7 +3668,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134600607</v>
+        <v>134600597</v>
       </c>
       <c r="B29" t="n">
         <v>80500</v>
@@ -3745,13 +3703,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618395</v>
+        <v>618280</v>
       </c>
       <c r="R29" t="n">
-        <v>7107952</v>
+        <v>7107895</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3780,7 +3738,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3790,7 +3748,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,7 +3779,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134600612</v>
+        <v>134600600</v>
       </c>
       <c r="B30" t="n">
         <v>80500</v>
@@ -3856,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618445</v>
+        <v>618343</v>
       </c>
       <c r="R30" t="n">
-        <v>7107999</v>
+        <v>7107901</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3891,7 +3849,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3859,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3921,7 +3879,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3932,32 +3890,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134600617</v>
+        <v>134600604</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3967,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618484</v>
+        <v>618391</v>
       </c>
       <c r="R31" t="n">
-        <v>7108085</v>
+        <v>7107940</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4002,7 +3960,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4012,12 +3970,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4037,7 +3990,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4048,32 +4001,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134600621</v>
+        <v>134600607</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4083,10 +4036,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618571</v>
+        <v>618395</v>
       </c>
       <c r="R32" t="n">
-        <v>7108018</v>
+        <v>7107952</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4118,7 +4071,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4128,12 +4081,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4153,7 +4101,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4164,32 +4112,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134600622</v>
+        <v>134600612</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4199,10 +4147,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>618510</v>
+        <v>618445</v>
       </c>
       <c r="R33" t="n">
-        <v>7107948</v>
+        <v>7107999</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4234,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4244,12 +4192,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4280,7 +4223,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134600623</v>
+        <v>134600617</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -4315,13 +4258,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>618504</v>
+        <v>618484</v>
       </c>
       <c r="R34" t="n">
-        <v>7107921</v>
+        <v>7108085</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4350,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,12 +4303,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4396,7 +4339,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134600624</v>
+        <v>134600621</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4431,10 +4374,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618502</v>
+        <v>618571</v>
       </c>
       <c r="R35" t="n">
-        <v>7107915</v>
+        <v>7108018</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4466,7 +4409,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,12 +4419,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4512,7 +4455,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134600626</v>
+        <v>134600622</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4541,24 +4484,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618506</v>
+        <v>618510</v>
       </c>
       <c r="R36" t="n">
-        <v>7107873</v>
+        <v>7107948</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4590,7 +4525,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4535,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4631,7 +4571,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134600627</v>
+        <v>134600623</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4666,13 +4606,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618494</v>
+        <v>618504</v>
       </c>
       <c r="R37" t="n">
-        <v>7107769</v>
+        <v>7107921</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4701,7 +4641,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4711,12 +4651,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,57 +4687,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134600614</v>
+        <v>134600624</v>
       </c>
       <c r="B38" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618441</v>
+        <v>618502</v>
       </c>
       <c r="R38" t="n">
-        <v>7108023</v>
+        <v>7107915</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4829,7 +4757,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4839,7 +4767,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,7 +4781,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4871,45 +4803,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134600599</v>
+        <v>134600626</v>
       </c>
       <c r="B39" t="n">
-        <v>99217</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618328</v>
+        <v>618506</v>
       </c>
       <c r="R39" t="n">
-        <v>7107905</v>
+        <v>7107873</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4941,7 +4881,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4951,7 +4891,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4971,7 +4911,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Sture Gustafsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4982,32 +4922,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134600629</v>
+        <v>134600627</v>
       </c>
       <c r="B40" t="n">
-        <v>99217</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5017,13 +4957,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618484</v>
+        <v>618494</v>
       </c>
       <c r="R40" t="n">
-        <v>7107716</v>
+        <v>7107769</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5052,7 +4992,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5062,7 +5002,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5093,10 +5038,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134600602</v>
+        <v>134767650</v>
       </c>
       <c r="B41" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5104,37 +5049,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Pellemyrtjärnen, Ås lm</t>
+          <t>Pellemyrtjärnen, Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>618350</v>
+        <v>618170</v>
       </c>
       <c r="R41" t="n">
-        <v>7107906</v>
+        <v>7107804</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5158,22 +5103,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5188,26 +5128,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134600603</v>
+        <v>134767696</v>
       </c>
       <c r="B42" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5215,37 +5151,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Pellemyrtjärnen, Ås lm</t>
+          <t>Pellemyrtjärnen, Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>618369</v>
+        <v>618191</v>
       </c>
       <c r="R42" t="n">
-        <v>7107927</v>
+        <v>7107739</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5269,22 +5205,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5299,61 +5230,69 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134600610</v>
+        <v>134600614</v>
       </c>
       <c r="B43" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>618432</v>
+        <v>618441</v>
       </c>
       <c r="R43" t="n">
-        <v>7107994</v>
+        <v>7108023</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5385,7 +5324,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5395,7 +5334,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5404,6 +5343,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5419,6 +5359,561 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134600599</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>618328</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7107905</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134600629</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>618484</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7107716</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134600602</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>618350</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7107906</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134600603</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>618369</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7107927</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134600610</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>618432</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7107994</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>

--- a/artfynd/A 10292-2023 artfynd.xlsx
+++ b/artfynd/A 10292-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600593</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600616</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600592</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600596</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600605</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600619</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600620</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600625</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134767608</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600591</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600601</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1990,6 +2050,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600618</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2104,6 +2169,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7242771</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2218,6 +2288,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7242772</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2332,6 +2407,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7242776</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2446,6 +2526,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7242778</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2560,6 +2645,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7242781</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2671,6 +2761,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600590</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2782,6 +2877,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600595</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2893,6 +2993,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600598</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3004,6 +3109,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600606</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3115,6 +3225,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600608</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3249,6 +3364,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600609</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3360,6 +3480,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600611</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3457,6 +3582,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134767657</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3554,6 +3684,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134767677</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3665,6 +3800,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600613</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3776,6 +3916,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600597</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3887,6 +4032,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600600</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3998,6 +4148,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600604</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4109,6 +4264,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600607</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4220,6 +4380,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600612</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4336,6 +4501,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600617</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4452,6 +4622,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600621</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4568,6 +4743,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600622</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4684,6 +4864,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600623</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4800,6 +4985,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600624</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4919,6 +5109,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600626</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5035,6 +5230,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600627</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5137,6 +5337,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134767650</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5239,6 +5444,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134767696</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5363,6 +5573,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600614</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5474,6 +5689,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600599</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5585,6 +5805,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600629</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5696,6 +5921,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600602</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5807,6 +6037,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600603</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5918,8 +6153,62 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600610</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>